--- a/Stock_OneClick/history/scan_result_20260602_121610.xlsx
+++ b/Stock_OneClick/history/scan_result_20260602_121610.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q217"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -667,24 +667,12 @@
       <c r="J3" s="4" t="n">
         <v>188.6</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-02; 相对D0=12.68%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -736,24 +724,12 @@
       <c r="J4" s="4" t="n">
         <v>48.8</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-02; 相对D0=1.41%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -805,24 +781,12 @@
       <c r="J5" s="4" t="n">
         <v>142.725</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-02; 相对D0=5.50%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -874,24 +838,12 @@
       <c r="J6" s="4" t="n">
         <v>139.05</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-02; 相对D0=-1.54%; 本次触发=2026-06-02(正式买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -943,24 +895,12 @@
       <c r="J7" s="4" t="n">
         <v>416.99</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-02; 相对D0=6.55%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1012,24 +952,6 @@
       <c r="J8" t="n">
         <v>23.445</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-02; 相对D0=4.15%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1081,24 +1003,12 @@
       <c r="J9" s="4" t="n">
         <v>133.8</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-02; 相对D0=-2.80%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1150,24 +1060,12 @@
       <c r="J10" s="4" t="n">
         <v>275.815</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-02; 相对D0=5.17%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -1219,24 +1117,6 @@
       <c r="J11" t="n">
         <v>56.81</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-02; 相对D0=3.40%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1288,24 +1168,6 @@
       <c r="J12" t="n">
         <v>88.3</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-02; 相对D0=8.00%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1357,27 +1219,15 @@
       <c r="J13" s="4" t="n">
         <v>15.3993</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>D0=13.02; 最新=2026-06-02; 相对D0=18.27%; 本次触发=2026-06-02(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
+          <t>D0=13.02; 最新=2026-06-02; 相对D0=18.27%; 本次触发=2026-06-02(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1426,24 +1276,12 @@
       <c r="J14" s="4" t="n">
         <v>158.405</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-02; 相对D0=1.37%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1495,24 +1333,6 @@
       <c r="J15" t="n">
         <v>51.49</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-02; 相对D0=2.39%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -1564,24 +1384,12 @@
       <c r="J16" s="4" t="n">
         <v>137.5</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-02; 相对D0=2.15%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -1633,24 +1441,12 @@
       <c r="J17" s="4" t="n">
         <v>72.565</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-02; 相对D0=5.63%; 本次触发=2026-06-02(预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -1702,27 +1498,15 @@
       <c r="J18" s="4" t="n">
         <v>19.36</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>D0=18.40; 最新=2026-06-02; 相对D0=5.22%; 本次触发=2026-06-02(正式买入 | 第一买入点 | 预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
+          <t>D0=18.40; 最新=2026-06-02; 相对D0=5.22%; 本次触发=2026-06-02(正式买入 | 第一观察点 | 预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1771,24 +1555,6 @@
       <c r="J19" t="n">
         <v>333.01</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-02; 相对D0=2.81%; 本次触发=2026-06-02(正式买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -1840,24 +1606,6 @@
       <c r="J20" t="n">
         <v>300.815</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-02; 相对D0=3.73%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1909,24 +1657,6 @@
       <c r="J21" t="n">
         <v>66.33499999999999</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-02; 相对D0=-1.55%; 本次触发=2026-06-02(正式买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -1978,24 +1708,12 @@
       <c r="J22" s="4" t="n">
         <v>390.46</v>
       </c>
-      <c r="K22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-02; 相对D0=4.31%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2047,24 +1765,6 @@
       <c r="J23" t="n">
         <v>51.555</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-02; 相对D0=-0.05%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2116,24 +1816,12 @@
       <c r="J24" s="4" t="n">
         <v>117.22</v>
       </c>
-      <c r="K24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-02; 相对D0=1.42%; 本次触发=2026-06-02(预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2185,24 +1873,12 @@
       <c r="J25" s="4" t="n">
         <v>188.06</v>
       </c>
-      <c r="K25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-02; 相对D0=1.20%; 本次触发=2026-06-02(正式买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2254,24 +1930,6 @@
       <c r="J26" t="n">
         <v>12.665</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-02; 相对D0=14.93%; 本次触发=2026-06-02(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-02</t>
@@ -2323,24 +1981,6 @@
       <c r="J27" t="n">
         <v>314.82</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=314.82; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -2392,24 +2032,12 @@
       <c r="J28" s="4" t="n">
         <v>112.31</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>D0=112.31; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2461,24 +2089,6 @@
       <c r="J29" t="n">
         <v>116.545</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=116.55; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2530,24 +2140,6 @@
       <c r="J30" t="n">
         <v>300.815</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=300.81; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2599,24 +2191,12 @@
       <c r="J31" s="4" t="n">
         <v>188.6</v>
       </c>
-      <c r="K31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>D0=188.60; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2668,24 +2248,6 @@
       <c r="J32" t="n">
         <v>421.3634</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=421.36; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -2737,24 +2299,12 @@
       <c r="J33" s="4" t="n">
         <v>117.22</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=117.22; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -2806,24 +2356,6 @@
       <c r="J34" t="n">
         <v>231.09</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=231.09; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -2875,24 +2407,12 @@
       <c r="J35" s="4" t="n">
         <v>188.06</v>
       </c>
-      <c r="K35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>D0=188.06; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -2944,24 +2464,6 @@
       <c r="J36" t="n">
         <v>66.33499999999999</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=66.33; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -3013,24 +2515,12 @@
       <c r="J37" s="4" t="n">
         <v>48.8</v>
       </c>
-      <c r="K37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>D0=48.80; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3082,24 +2572,6 @@
       <c r="J38" t="n">
         <v>72.48</v>
       </c>
-      <c r="K38" t="n">
-        <v/>
-      </c>
-      <c r="L38" t="n">
-        <v/>
-      </c>
-      <c r="M38" t="n">
-        <v/>
-      </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
-      <c r="O38" t="n">
-        <v/>
-      </c>
-      <c r="P38" t="n">
-        <v/>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>D0=72.48; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3151,24 +2623,12 @@
       <c r="J39" s="4" t="n">
         <v>142.725</v>
       </c>
-      <c r="K39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>D0=142.72; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3220,24 +2680,12 @@
       <c r="J40" s="4" t="n">
         <v>139.05</v>
       </c>
-      <c r="K40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>D0=139.05; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -3289,24 +2737,12 @@
       <c r="J41" s="4" t="n">
         <v>416.99</v>
       </c>
-      <c r="K41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>D0=416.99; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3358,24 +2794,6 @@
       <c r="J42" t="n">
         <v>198.21</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=198.21; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3427,24 +2845,12 @@
       <c r="J43" s="4" t="n">
         <v>40.03</v>
       </c>
-      <c r="K43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>D0=40.03; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3496,24 +2902,6 @@
       <c r="J44" t="n">
         <v>12.665</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=12.66; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3565,24 +2953,6 @@
       <c r="J45" t="n">
         <v>11.65</v>
       </c>
-      <c r="K45" t="n">
-        <v/>
-      </c>
-      <c r="L45" t="n">
-        <v/>
-      </c>
-      <c r="M45" t="n">
-        <v/>
-      </c>
-      <c r="N45" t="n">
-        <v/>
-      </c>
-      <c r="O45" t="n">
-        <v/>
-      </c>
-      <c r="P45" t="n">
-        <v/>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>D0=11.65; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3634,24 +3004,6 @@
       <c r="J46" t="n">
         <v>23.445</v>
       </c>
-      <c r="K46" t="n">
-        <v/>
-      </c>
-      <c r="L46" t="n">
-        <v/>
-      </c>
-      <c r="M46" t="n">
-        <v/>
-      </c>
-      <c r="N46" t="n">
-        <v/>
-      </c>
-      <c r="O46" t="n">
-        <v/>
-      </c>
-      <c r="P46" t="n">
-        <v/>
-      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>D0=23.45; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3703,24 +3055,12 @@
       <c r="J47" s="4" t="n">
         <v>137.5</v>
       </c>
-      <c r="K47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>D0=137.50; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -3772,24 +3112,12 @@
       <c r="J48" s="4" t="n">
         <v>133.8</v>
       </c>
-      <c r="K48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>D0=133.80; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3841,24 +3169,12 @@
       <c r="J49" s="4" t="n">
         <v>25.78</v>
       </c>
-      <c r="K49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>D0=25.78; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -3910,24 +3226,12 @@
       <c r="J50" s="4" t="n">
         <v>72.565</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=72.56; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -3979,24 +3283,12 @@
       <c r="J51" s="4" t="n">
         <v>275.815</v>
       </c>
-      <c r="K51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>D0=275.81; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4048,24 +3340,6 @@
       <c r="J52" t="n">
         <v>56.81</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=56.81; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4117,24 +3391,12 @@
       <c r="J53" s="4" t="n">
         <v>56.3601</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>D0=56.36; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4186,24 +3448,6 @@
       <c r="J54" t="n">
         <v>504.3</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>D0=504.30; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4255,24 +3499,6 @@
       <c r="J55" t="n">
         <v>88.3</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=88.30; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4324,24 +3550,12 @@
       <c r="J56" s="4" t="n">
         <v>390.46</v>
       </c>
-      <c r="K56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>D0=390.46; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4393,24 +3607,12 @@
       <c r="J57" s="4" t="n">
         <v>386.665</v>
       </c>
-      <c r="K57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>D0=386.67; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4462,24 +3664,6 @@
       <c r="J58" t="n">
         <v>274.07</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=274.07; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4531,27 +3715,15 @@
       <c r="J59" s="4" t="n">
         <v>15.3993</v>
       </c>
-      <c r="K59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>D0=15.40; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=15.40; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -4600,27 +3772,15 @@
       <c r="J60" s="4" t="n">
         <v>19.36</v>
       </c>
-      <c r="K60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="inlineStr">
         <is>
-          <t>D0=19.36; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=19.36; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -4669,24 +3829,6 @@
       <c r="J61" t="n">
         <v>333.01</v>
       </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
-      <c r="L61" t="n">
-        <v/>
-      </c>
-      <c r="M61" t="n">
-        <v/>
-      </c>
-      <c r="N61" t="n">
-        <v/>
-      </c>
-      <c r="O61" t="n">
-        <v/>
-      </c>
-      <c r="P61" t="n">
-        <v/>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>D0=333.01; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入)</t>
@@ -4738,24 +3880,12 @@
       <c r="J62" s="4" t="n">
         <v>158.405</v>
       </c>
-      <c r="K62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="inlineStr">
         <is>
           <t>D0=158.41; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4807,24 +3937,6 @@
       <c r="J63" t="n">
         <v>51.49</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>D0=51.49; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(预警买入)</t>
@@ -4876,24 +3988,12 @@
       <c r="J64" s="4" t="n">
         <v>58.075</v>
       </c>
-      <c r="K64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="n"/>
+      <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="inlineStr">
         <is>
           <t>D0=58.08; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -4945,24 +4045,6 @@
       <c r="J65" t="n">
         <v>51.555</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
-      <c r="L65" t="n">
-        <v/>
-      </c>
-      <c r="M65" t="n">
-        <v/>
-      </c>
-      <c r="N65" t="n">
-        <v/>
-      </c>
-      <c r="O65" t="n">
-        <v/>
-      </c>
-      <c r="P65" t="n">
-        <v/>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>D0=51.55; 最新=2026-06-02; 相对D0=0.00%; 本次触发=2026-06-02(正式买入 | 预警买入)</t>
@@ -5014,24 +4096,6 @@
       <c r="J66" t="n">
         <v>201.55</v>
       </c>
-      <c r="K66" t="n">
-        <v/>
-      </c>
-      <c r="L66" t="n">
-        <v/>
-      </c>
-      <c r="M66" t="n">
-        <v/>
-      </c>
-      <c r="N66" t="n">
-        <v/>
-      </c>
-      <c r="O66" t="n">
-        <v/>
-      </c>
-      <c r="P66" t="n">
-        <v/>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-02; 相对D0=11.05%; 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -5083,24 +4147,12 @@
       <c r="J67" s="4" t="n">
         <v>185.03</v>
       </c>
-      <c r="K67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-02; 相对D0=-8.81%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -5152,24 +4204,12 @@
       <c r="J68" s="4" t="n">
         <v>273.12</v>
       </c>
-      <c r="K68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-02; 相对D0=-7.12%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -5221,24 +4261,12 @@
       <c r="J69" s="4" t="n">
         <v>57.62</v>
       </c>
-      <c r="K69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-02; 相对D0=23.83%</t>
@@ -5290,24 +4318,6 @@
       <c r="J70" t="n">
         <v>16.675</v>
       </c>
-      <c r="K70" t="n">
-        <v/>
-      </c>
-      <c r="L70" t="n">
-        <v/>
-      </c>
-      <c r="M70" t="n">
-        <v/>
-      </c>
-      <c r="N70" t="n">
-        <v/>
-      </c>
-      <c r="O70" t="n">
-        <v/>
-      </c>
-      <c r="P70" t="n">
-        <v/>
-      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-02; 相对D0=3.44%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -5359,24 +4369,12 @@
       <c r="J71" s="4" t="n">
         <v>199.64</v>
       </c>
-      <c r="K71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-02; 相对D0=10.87%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -5428,24 +4426,12 @@
       <c r="J72" s="4" t="n">
         <v>966.765</v>
       </c>
-      <c r="K72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-02; 相对D0=-6.93%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -5497,24 +4483,6 @@
       <c r="J73" t="n">
         <v>49.81</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-02; 相对D0=-1.68%; 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -5566,24 +4534,12 @@
       <c r="J74" s="4" t="n">
         <v>199.13</v>
       </c>
-      <c r="K74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-02; 相对D0=11.02%; 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
@@ -5635,24 +4591,12 @@
       <c r="J75" s="4" t="n">
         <v>398.56</v>
       </c>
-      <c r="K75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P75" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-02; 相对D0=22.21%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -5704,24 +4648,6 @@
       <c r="J76" t="n">
         <v>600.4499</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-02; 相对D0=-1.61%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -5773,24 +4699,12 @@
       <c r="J77" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="K77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-02; 相对D0=13.73%</t>
@@ -5842,24 +4756,6 @@
       <c r="J78" t="n">
         <v>259.08</v>
       </c>
-      <c r="K78" t="n">
-        <v/>
-      </c>
-      <c r="L78" t="n">
-        <v/>
-      </c>
-      <c r="M78" t="n">
-        <v/>
-      </c>
-      <c r="N78" t="n">
-        <v/>
-      </c>
-      <c r="O78" t="n">
-        <v/>
-      </c>
-      <c r="P78" t="n">
-        <v/>
-      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-02; 相对D0=11.67%</t>
@@ -5911,24 +4807,6 @@
       <c r="J79" t="n">
         <v>151.52</v>
       </c>
-      <c r="K79" t="n">
-        <v/>
-      </c>
-      <c r="L79" t="n">
-        <v/>
-      </c>
-      <c r="M79" t="n">
-        <v/>
-      </c>
-      <c r="N79" t="n">
-        <v/>
-      </c>
-      <c r="O79" t="n">
-        <v/>
-      </c>
-      <c r="P79" t="n">
-        <v/>
-      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-02; 相对D0=16.11%</t>
@@ -5980,24 +4858,12 @@
       <c r="J80" s="4" t="n">
         <v>59.305</v>
       </c>
-      <c r="K80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P80" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-02; 相对D0=0.84%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -6049,24 +4915,12 @@
       <c r="J81" s="4" t="n">
         <v>108.53</v>
       </c>
-      <c r="K81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P81" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-02; 相对D0=27.05%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -6118,24 +4972,6 @@
       <c r="J82" t="n">
         <v>420.4075</v>
       </c>
-      <c r="K82" t="n">
-        <v/>
-      </c>
-      <c r="L82" t="n">
-        <v/>
-      </c>
-      <c r="M82" t="n">
-        <v/>
-      </c>
-      <c r="N82" t="n">
-        <v/>
-      </c>
-      <c r="O82" t="n">
-        <v/>
-      </c>
-      <c r="P82" t="n">
-        <v/>
-      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-02; 相对D0=-1.32%</t>
@@ -6187,24 +5023,6 @@
       <c r="J83" t="n">
         <v>375.41</v>
       </c>
-      <c r="K83" t="n">
-        <v/>
-      </c>
-      <c r="L83" t="n">
-        <v/>
-      </c>
-      <c r="M83" t="n">
-        <v/>
-      </c>
-      <c r="N83" t="n">
-        <v/>
-      </c>
-      <c r="O83" t="n">
-        <v/>
-      </c>
-      <c r="P83" t="n">
-        <v/>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-02; 相对D0=-3.36%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -6256,24 +5074,12 @@
       <c r="J84" s="4" t="n">
         <v>75.175</v>
       </c>
-      <c r="K84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="4" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n"/>
+      <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-02; 相对D0=2.33%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -6325,24 +5131,6 @@
       <c r="J85" t="n">
         <v>477.29</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-02; 相对D0=13.10%</t>
@@ -6394,24 +5182,6 @@
       <c r="J86" t="n">
         <v>93.19</v>
       </c>
-      <c r="K86" t="n">
-        <v/>
-      </c>
-      <c r="L86" t="n">
-        <v/>
-      </c>
-      <c r="M86" t="n">
-        <v/>
-      </c>
-      <c r="N86" t="n">
-        <v/>
-      </c>
-      <c r="O86" t="n">
-        <v/>
-      </c>
-      <c r="P86" t="n">
-        <v/>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-02; 相对D0=7.75%</t>
@@ -6463,24 +5233,12 @@
       <c r="J87" s="4" t="n">
         <v>185.03</v>
       </c>
-      <c r="K87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="4" t="n"/>
+      <c r="L87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="n"/>
+      <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-02; 相对D0=-9.47%</t>
@@ -6532,24 +5290,12 @@
       <c r="J88" s="4" t="n">
         <v>188.6</v>
       </c>
-      <c r="K88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="4" t="n"/>
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="n"/>
+      <c r="P88" s="4" t="n"/>
       <c r="Q88" s="4" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-02; 相对D0=7.94%</t>
@@ -6601,24 +5347,12 @@
       <c r="J89" s="4" t="n">
         <v>120.685</v>
       </c>
-      <c r="K89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-02; 相对D0=11.57%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6670,24 +5404,6 @@
       <c r="J90" t="n">
         <v>119.2</v>
       </c>
-      <c r="K90" t="n">
-        <v/>
-      </c>
-      <c r="L90" t="n">
-        <v/>
-      </c>
-      <c r="M90" t="n">
-        <v/>
-      </c>
-      <c r="N90" t="n">
-        <v/>
-      </c>
-      <c r="O90" t="n">
-        <v/>
-      </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-02; 相对D0=12.57%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -6739,24 +5455,12 @@
       <c r="J91" s="4" t="n">
         <v>48.8</v>
       </c>
-      <c r="K91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P91" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K91" s="4" t="n"/>
+      <c r="L91" s="4" t="n"/>
+      <c r="M91" s="4" t="n"/>
+      <c r="N91" s="4" t="n"/>
+      <c r="O91" s="4" t="n"/>
+      <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-02; 相对D0=-1.33%</t>
@@ -6808,24 +5512,12 @@
       <c r="J92" s="4" t="n">
         <v>416.99</v>
       </c>
-      <c r="K92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="4" t="n"/>
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="4" t="n"/>
+      <c r="N92" s="4" t="n"/>
+      <c r="O92" s="4" t="n"/>
+      <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-02; 相对D0=3.44%</t>
@@ -6877,24 +5569,12 @@
       <c r="J93" s="4" t="n">
         <v>966.765</v>
       </c>
-      <c r="K93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-02; 相对D0=-9.69%</t>
@@ -6946,24 +5626,6 @@
       <c r="J94" t="n">
         <v>363.99</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-02; 相对D0=-6.40%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -7015,24 +5677,12 @@
       <c r="J95" s="4" t="n">
         <v>199.13</v>
       </c>
-      <c r="K95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P95" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="n"/>
+      <c r="P95" s="4" t="n"/>
       <c r="Q95" s="4" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-02; 相对D0=8.60%</t>
@@ -7084,24 +5734,6 @@
       <c r="J96" t="n">
         <v>69.28</v>
       </c>
-      <c r="K96" t="n">
-        <v/>
-      </c>
-      <c r="L96" t="n">
-        <v/>
-      </c>
-      <c r="M96" t="n">
-        <v/>
-      </c>
-      <c r="N96" t="n">
-        <v/>
-      </c>
-      <c r="O96" t="n">
-        <v/>
-      </c>
-      <c r="P96" t="n">
-        <v/>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-02; 相对D0=-0.50%</t>
@@ -7153,24 +5785,6 @@
       <c r="J97" t="n">
         <v>600.4499</v>
       </c>
-      <c r="K97" t="n">
-        <v/>
-      </c>
-      <c r="L97" t="n">
-        <v/>
-      </c>
-      <c r="M97" t="n">
-        <v/>
-      </c>
-      <c r="N97" t="n">
-        <v/>
-      </c>
-      <c r="O97" t="n">
-        <v/>
-      </c>
-      <c r="P97" t="n">
-        <v/>
-      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-02; 相对D0=-1.94%</t>
@@ -7222,24 +5836,6 @@
       <c r="J98" t="n">
         <v>23.445</v>
       </c>
-      <c r="K98" t="n">
-        <v/>
-      </c>
-      <c r="L98" t="n">
-        <v/>
-      </c>
-      <c r="M98" t="n">
-        <v/>
-      </c>
-      <c r="N98" t="n">
-        <v/>
-      </c>
-      <c r="O98" t="n">
-        <v/>
-      </c>
-      <c r="P98" t="n">
-        <v/>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-02; 相对D0=3.65%</t>
@@ -7291,24 +5887,12 @@
       <c r="J99" s="4" t="n">
         <v>275.815</v>
       </c>
-      <c r="K99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P99" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K99" s="4" t="n"/>
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="4" t="n"/>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="n"/>
+      <c r="P99" s="4" t="n"/>
       <c r="Q99" s="4" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-02; 相对D0=0.60%</t>
@@ -7360,24 +5944,6 @@
       <c r="J100" t="n">
         <v>56.81</v>
       </c>
-      <c r="K100" t="n">
-        <v/>
-      </c>
-      <c r="L100" t="n">
-        <v/>
-      </c>
-      <c r="M100" t="n">
-        <v/>
-      </c>
-      <c r="N100" t="n">
-        <v/>
-      </c>
-      <c r="O100" t="n">
-        <v/>
-      </c>
-      <c r="P100" t="n">
-        <v/>
-      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-02; 相对D0=0.89%</t>
@@ -7429,24 +5995,6 @@
       <c r="J101" t="n">
         <v>111.92</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-02; 相对D0=4.66%</t>
@@ -7498,24 +6046,12 @@
       <c r="J102" s="4" t="n">
         <v>13.995</v>
       </c>
-      <c r="K102" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L102" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M102" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N102" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O102" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P102" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="4" t="n"/>
+      <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="n"/>
+      <c r="P102" s="4" t="n"/>
       <c r="Q102" s="4" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-02; 相对D0=14.53%</t>
@@ -7567,24 +6103,6 @@
       <c r="J103" t="n">
         <v>17.6049</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-02; 相对D0=10.17%</t>
@@ -7636,24 +6154,6 @@
       <c r="J104" t="n">
         <v>88.3</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-02; 相对D0=4.32%</t>
@@ -7705,24 +6205,12 @@
       <c r="J105" s="4" t="n">
         <v>15.3993</v>
       </c>
-      <c r="K105" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="4" t="n"/>
+      <c r="L105" s="4" t="n"/>
+      <c r="M105" s="4" t="n"/>
+      <c r="N105" s="4" t="n"/>
+      <c r="O105" s="4" t="n"/>
+      <c r="P105" s="4" t="n"/>
       <c r="Q105" s="4" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-02; 相对D0=13.98%</t>
@@ -7774,24 +6262,6 @@
       <c r="J106" t="n">
         <v>51.49</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-02; 相对D0=0.98%</t>
@@ -7843,24 +6313,6 @@
       <c r="J107" t="n">
         <v>201.55</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-02; 相对D0=12.08%</t>
@@ -7912,24 +6364,6 @@
       <c r="J108" t="n">
         <v>258.065</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-02; 相对D0=-5.07%</t>
@@ -7950,7 +6384,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7977,24 +6410,6 @@
       <c r="J109" t="n">
         <v>89.095</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-02; 相对D0=-1.95%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -8046,24 +6461,6 @@
       <c r="J110" t="n">
         <v>16.675</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-02; 相对D0=1.31%</t>
@@ -8115,24 +6512,6 @@
       <c r="J111" t="n">
         <v>27.29</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-02; 相对D0=8.29%</t>
@@ -8184,24 +6563,6 @@
       <c r="J112" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="K112" t="n">
-        <v/>
-      </c>
-      <c r="L112" t="n">
-        <v/>
-      </c>
-      <c r="M112" t="n">
-        <v/>
-      </c>
-      <c r="N112" t="n">
-        <v/>
-      </c>
-      <c r="O112" t="n">
-        <v/>
-      </c>
-      <c r="P112" t="n">
-        <v/>
-      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-02; 相对D0=14.92%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -8253,24 +6614,6 @@
       <c r="J113" t="n">
         <v>49.81</v>
       </c>
-      <c r="K113" t="n">
-        <v/>
-      </c>
-      <c r="L113" t="n">
-        <v/>
-      </c>
-      <c r="M113" t="n">
-        <v/>
-      </c>
-      <c r="N113" t="n">
-        <v/>
-      </c>
-      <c r="O113" t="n">
-        <v/>
-      </c>
-      <c r="P113" t="n">
-        <v/>
-      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-02; 相对D0=-1.25%</t>
@@ -8322,24 +6665,12 @@
       <c r="J114" s="4" t="n">
         <v>127.23</v>
       </c>
-      <c r="K114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
       <c r="Q114" s="4" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-02; 相对D0=24.59%</t>
@@ -8391,24 +6722,12 @@
       <c r="J115" s="4" t="n">
         <v>275.815</v>
       </c>
-      <c r="K115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P115" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
       <c r="Q115" s="4" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-02; 相对D0=3.34%</t>
@@ -8460,24 +6779,6 @@
       <c r="J116" t="n">
         <v>243.58</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-02; 相对D0=27.56%</t>
@@ -8529,24 +6830,12 @@
       <c r="J117" s="4" t="n">
         <v>108.53</v>
       </c>
-      <c r="K117" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L117" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M117" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N117" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O117" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P117" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="n"/>
+      <c r="M117" s="4" t="n"/>
+      <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="n"/>
+      <c r="P117" s="4" t="n"/>
       <c r="Q117" s="4" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-02; 相对D0=21.85%</t>
@@ -8598,24 +6887,6 @@
       <c r="J118" t="n">
         <v>375.41</v>
       </c>
-      <c r="K118" t="n">
-        <v/>
-      </c>
-      <c r="L118" t="n">
-        <v/>
-      </c>
-      <c r="M118" t="n">
-        <v/>
-      </c>
-      <c r="N118" t="n">
-        <v/>
-      </c>
-      <c r="O118" t="n">
-        <v/>
-      </c>
-      <c r="P118" t="n">
-        <v/>
-      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-02; 相对D0=-2.24%</t>
@@ -8636,7 +6907,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8663,24 +6933,6 @@
       <c r="J119" t="n">
         <v>89.095</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-02; 相对D0=-2.19%</t>
@@ -8732,24 +6984,12 @@
       <c r="J120" s="4" t="n">
         <v>120.685</v>
       </c>
-      <c r="K120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P120" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-02; 相对D0=9.09%</t>
@@ -8801,24 +7041,6 @@
       <c r="J121" t="n">
         <v>93.98</v>
       </c>
-      <c r="K121" t="n">
-        <v/>
-      </c>
-      <c r="L121" t="n">
-        <v/>
-      </c>
-      <c r="M121" t="n">
-        <v/>
-      </c>
-      <c r="N121" t="n">
-        <v/>
-      </c>
-      <c r="O121" t="n">
-        <v/>
-      </c>
-      <c r="P121" t="n">
-        <v/>
-      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-02; 相对D0=12.31%</t>
@@ -8870,24 +7092,12 @@
       <c r="J122" s="4" t="n">
         <v>199.64</v>
       </c>
-      <c r="K122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P122" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
+      <c r="O122" s="4" t="n"/>
+      <c r="P122" s="4" t="n"/>
       <c r="Q122" s="4" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-02; 相对D0=13.32%</t>
@@ -8939,24 +7149,6 @@
       <c r="J123" t="n">
         <v>763.575</v>
       </c>
-      <c r="K123" t="n">
-        <v/>
-      </c>
-      <c r="L123" t="n">
-        <v/>
-      </c>
-      <c r="M123" t="n">
-        <v/>
-      </c>
-      <c r="N123" t="n">
-        <v/>
-      </c>
-      <c r="O123" t="n">
-        <v/>
-      </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-02; 相对D0=13.80%</t>
@@ -9008,24 +7200,6 @@
       <c r="J124" t="n">
         <v>119.2</v>
       </c>
-      <c r="K124" t="n">
-        <v/>
-      </c>
-      <c r="L124" t="n">
-        <v/>
-      </c>
-      <c r="M124" t="n">
-        <v/>
-      </c>
-      <c r="N124" t="n">
-        <v/>
-      </c>
-      <c r="O124" t="n">
-        <v/>
-      </c>
-      <c r="P124" t="n">
-        <v/>
-      </c>
       <c r="Q124" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-02; 相对D0=11.55%</t>
@@ -9046,7 +7220,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -9073,24 +7246,6 @@
       <c r="J125" t="n">
         <v>1071.165</v>
       </c>
-      <c r="K125" t="n">
-        <v/>
-      </c>
-      <c r="L125" t="n">
-        <v/>
-      </c>
-      <c r="M125" t="n">
-        <v/>
-      </c>
-      <c r="N125" t="n">
-        <v/>
-      </c>
-      <c r="O125" t="n">
-        <v/>
-      </c>
-      <c r="P125" t="n">
-        <v/>
-      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-02; 相对D0=0.16%</t>
@@ -9142,24 +7297,6 @@
       <c r="J126" t="n">
         <v>147.135</v>
       </c>
-      <c r="K126" t="n">
-        <v/>
-      </c>
-      <c r="L126" t="n">
-        <v/>
-      </c>
-      <c r="M126" t="n">
-        <v/>
-      </c>
-      <c r="N126" t="n">
-        <v/>
-      </c>
-      <c r="O126" t="n">
-        <v/>
-      </c>
-      <c r="P126" t="n">
-        <v/>
-      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-02; 相对D0=13.44%</t>
@@ -9211,24 +7348,6 @@
       <c r="J127" t="n">
         <v>363.99</v>
       </c>
-      <c r="K127" t="n">
-        <v/>
-      </c>
-      <c r="L127" t="n">
-        <v/>
-      </c>
-      <c r="M127" t="n">
-        <v/>
-      </c>
-      <c r="N127" t="n">
-        <v/>
-      </c>
-      <c r="O127" t="n">
-        <v/>
-      </c>
-      <c r="P127" t="n">
-        <v/>
-      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-02; 相对D0=-6.70%</t>
@@ -9280,24 +7399,6 @@
       <c r="J128" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="K128" t="n">
-        <v/>
-      </c>
-      <c r="L128" t="n">
-        <v/>
-      </c>
-      <c r="M128" t="n">
-        <v/>
-      </c>
-      <c r="N128" t="n">
-        <v/>
-      </c>
-      <c r="O128" t="n">
-        <v/>
-      </c>
-      <c r="P128" t="n">
-        <v/>
-      </c>
       <c r="Q128" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-02; 相对D0=3.25%</t>
@@ -9349,24 +7450,12 @@
       <c r="J129" s="4" t="n">
         <v>104.36</v>
       </c>
-      <c r="K129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
+      <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
       <c r="Q129" s="4" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-02; 相对D0=9.07%</t>
@@ -9418,24 +7507,12 @@
       <c r="J130" s="4" t="n">
         <v>199.13</v>
       </c>
-      <c r="K130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K130" s="4" t="n"/>
+      <c r="L130" s="4" t="n"/>
+      <c r="M130" s="4" t="n"/>
+      <c r="N130" s="4" t="n"/>
+      <c r="O130" s="4" t="n"/>
+      <c r="P130" s="4" t="n"/>
       <c r="Q130" s="4" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-02; 相对D0=7.37%</t>
@@ -9487,24 +7564,12 @@
       <c r="J131" s="4" t="n">
         <v>398.56</v>
       </c>
-      <c r="K131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K131" s="4" t="n"/>
+      <c r="L131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
+      <c r="P131" s="4" t="n"/>
       <c r="Q131" s="4" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-02; 相对D0=22.38%</t>
@@ -9556,24 +7621,6 @@
       <c r="J132" t="n">
         <v>441.76</v>
       </c>
-      <c r="K132" t="n">
-        <v/>
-      </c>
-      <c r="L132" t="n">
-        <v/>
-      </c>
-      <c r="M132" t="n">
-        <v/>
-      </c>
-      <c r="N132" t="n">
-        <v/>
-      </c>
-      <c r="O132" t="n">
-        <v/>
-      </c>
-      <c r="P132" t="n">
-        <v/>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-02; 相对D0=3.46%</t>
@@ -9625,24 +7672,6 @@
       <c r="J133" t="n">
         <v>261.775</v>
       </c>
-      <c r="K133" t="n">
-        <v/>
-      </c>
-      <c r="L133" t="n">
-        <v/>
-      </c>
-      <c r="M133" t="n">
-        <v/>
-      </c>
-      <c r="N133" t="n">
-        <v/>
-      </c>
-      <c r="O133" t="n">
-        <v/>
-      </c>
-      <c r="P133" t="n">
-        <v/>
-      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-02; 相对D0=15.66%</t>
@@ -9694,24 +7723,12 @@
       <c r="J134" s="4" t="n">
         <v>137.5</v>
       </c>
-      <c r="K134" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L134" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M134" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N134" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O134" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P134" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K134" s="4" t="n"/>
+      <c r="L134" s="4" t="n"/>
+      <c r="M134" s="4" t="n"/>
+      <c r="N134" s="4" t="n"/>
+      <c r="O134" s="4" t="n"/>
+      <c r="P134" s="4" t="n"/>
       <c r="Q134" s="4" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-02; 相对D0=3.14%</t>
@@ -9763,24 +7780,6 @@
       <c r="J135" t="n">
         <v>135.9894</v>
       </c>
-      <c r="K135" t="n">
-        <v/>
-      </c>
-      <c r="L135" t="n">
-        <v/>
-      </c>
-      <c r="M135" t="n">
-        <v/>
-      </c>
-      <c r="N135" t="n">
-        <v/>
-      </c>
-      <c r="O135" t="n">
-        <v/>
-      </c>
-      <c r="P135" t="n">
-        <v/>
-      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-02; 相对D0=43.57%</t>
@@ -9832,24 +7831,6 @@
       <c r="J136" t="n">
         <v>294.75</v>
       </c>
-      <c r="K136" t="n">
-        <v/>
-      </c>
-      <c r="L136" t="n">
-        <v/>
-      </c>
-      <c r="M136" t="n">
-        <v/>
-      </c>
-      <c r="N136" t="n">
-        <v/>
-      </c>
-      <c r="O136" t="n">
-        <v/>
-      </c>
-      <c r="P136" t="n">
-        <v/>
-      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-02; 相对D0=14.35%</t>
@@ -9901,24 +7882,12 @@
       <c r="J137" s="4" t="n">
         <v>152.36</v>
       </c>
-      <c r="K137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
       <c r="Q137" s="4" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-02; 相对D0=6.29%</t>
@@ -9970,24 +7939,12 @@
       <c r="J138" s="4" t="n">
         <v>261.565</v>
       </c>
-      <c r="K138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K138" s="4" t="n"/>
+      <c r="L138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
+      <c r="N138" s="4" t="n"/>
+      <c r="O138" s="4" t="n"/>
+      <c r="P138" s="4" t="n"/>
       <c r="Q138" s="4" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-02; 相对D0=0.91%</t>
@@ -10039,24 +7996,12 @@
       <c r="J139" s="4" t="n">
         <v>188.6</v>
       </c>
-      <c r="K139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P139" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K139" s="4" t="n"/>
+      <c r="L139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
+      <c r="P139" s="4" t="n"/>
       <c r="Q139" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-02; 相对D0=9.87%</t>
@@ -10108,24 +8053,12 @@
       <c r="J140" s="4" t="n">
         <v>273.12</v>
       </c>
-      <c r="K140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
       <c r="Q140" s="4" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-02; 相对D0=-5.08%</t>
@@ -10177,24 +8110,6 @@
       <c r="J141" t="n">
         <v>172.68</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-02; 相对D0=-8.65%</t>
@@ -10246,24 +8161,12 @@
       <c r="J142" s="4" t="n">
         <v>199.64</v>
       </c>
-      <c r="K142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P142" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
+      <c r="N142" s="4" t="n"/>
+      <c r="O142" s="4" t="n"/>
+      <c r="P142" s="4" t="n"/>
       <c r="Q142" s="4" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-02; 相对D0=4.47%</t>
@@ -10315,24 +8218,6 @@
       <c r="J143" t="n">
         <v>119.2</v>
       </c>
-      <c r="K143" t="n">
-        <v/>
-      </c>
-      <c r="L143" t="n">
-        <v/>
-      </c>
-      <c r="M143" t="n">
-        <v/>
-      </c>
-      <c r="N143" t="n">
-        <v/>
-      </c>
-      <c r="O143" t="n">
-        <v/>
-      </c>
-      <c r="P143" t="n">
-        <v/>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-02; 相对D0=8.83%</t>
@@ -10384,24 +8269,12 @@
       <c r="J144" s="4" t="n">
         <v>48.8</v>
       </c>
-      <c r="K144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P144" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K144" s="4" t="n"/>
+      <c r="L144" s="4" t="n"/>
+      <c r="M144" s="4" t="n"/>
+      <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
+      <c r="P144" s="4" t="n"/>
       <c r="Q144" s="4" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-02; 相对D0=0.78%</t>
@@ -10453,24 +8326,6 @@
       <c r="J145" t="n">
         <v>2037.3</v>
       </c>
-      <c r="K145" t="n">
-        <v/>
-      </c>
-      <c r="L145" t="n">
-        <v/>
-      </c>
-      <c r="M145" t="n">
-        <v/>
-      </c>
-      <c r="N145" t="n">
-        <v/>
-      </c>
-      <c r="O145" t="n">
-        <v/>
-      </c>
-      <c r="P145" t="n">
-        <v/>
-      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-02; 相对D0=6.01%</t>
@@ -10522,24 +8377,12 @@
       <c r="J146" s="4" t="n">
         <v>398.56</v>
       </c>
-      <c r="K146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P146" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
       <c r="Q146" s="4" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-02; 相对D0=18.78%</t>
@@ -10591,24 +8434,6 @@
       <c r="J147" t="n">
         <v>222.7801</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-02; 相对D0=5.51%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -10660,24 +8485,12 @@
       <c r="J148" s="4" t="n">
         <v>15.3993</v>
       </c>
-      <c r="K148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P148" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K148" s="4" t="n"/>
+      <c r="L148" s="4" t="n"/>
+      <c r="M148" s="4" t="n"/>
+      <c r="N148" s="4" t="n"/>
+      <c r="O148" s="4" t="n"/>
+      <c r="P148" s="4" t="n"/>
       <c r="Q148" s="4" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-02; 相对D0=11.83%</t>
@@ -10729,24 +8542,6 @@
       <c r="J149" t="n">
         <v>201.55</v>
       </c>
-      <c r="K149" t="n">
-        <v/>
-      </c>
-      <c r="L149" t="n">
-        <v/>
-      </c>
-      <c r="M149" t="n">
-        <v/>
-      </c>
-      <c r="N149" t="n">
-        <v/>
-      </c>
-      <c r="O149" t="n">
-        <v/>
-      </c>
-      <c r="P149" t="n">
-        <v/>
-      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-02; 相对D0=8.55%</t>
@@ -10798,24 +8593,12 @@
       <c r="J150" s="4" t="n">
         <v>14.705</v>
       </c>
-      <c r="K150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
+      <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="4" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-02; 相对D0=0.03%</t>
@@ -10867,24 +8650,12 @@
       <c r="J151" s="4" t="n">
         <v>75.175</v>
       </c>
-      <c r="K151" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L151" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M151" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N151" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O151" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P151" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K151" s="4" t="n"/>
+      <c r="L151" s="4" t="n"/>
+      <c r="M151" s="4" t="n"/>
+      <c r="N151" s="4" t="n"/>
+      <c r="O151" s="4" t="n"/>
+      <c r="P151" s="4" t="n"/>
       <c r="Q151" s="4" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-02; 相对D0=3.33%</t>
@@ -10936,24 +8707,6 @@
       <c r="J152" t="n">
         <v>318.055</v>
       </c>
-      <c r="K152" t="n">
-        <v/>
-      </c>
-      <c r="L152" t="n">
-        <v/>
-      </c>
-      <c r="M152" t="n">
-        <v/>
-      </c>
-      <c r="N152" t="n">
-        <v/>
-      </c>
-      <c r="O152" t="n">
-        <v/>
-      </c>
-      <c r="P152" t="n">
-        <v/>
-      </c>
       <c r="Q152" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-02; 相对D0=-0.73%</t>
@@ -11005,24 +8758,12 @@
       <c r="J153" s="4" t="n">
         <v>139.05</v>
       </c>
-      <c r="K153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P153" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K153" s="4" t="n"/>
+      <c r="L153" s="4" t="n"/>
+      <c r="M153" s="4" t="n"/>
+      <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
+      <c r="P153" s="4" t="n"/>
       <c r="Q153" s="4" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-02; 相对D0=1.78%</t>
@@ -11074,24 +8815,6 @@
       <c r="J154" t="n">
         <v>9.494999999999999</v>
       </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="n">
-        <v/>
-      </c>
-      <c r="M154" t="n">
-        <v/>
-      </c>
-      <c r="N154" t="n">
-        <v/>
-      </c>
-      <c r="O154" t="n">
-        <v/>
-      </c>
-      <c r="P154" t="n">
-        <v/>
-      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-02; 相对D0=5.85%</t>
@@ -11143,24 +8866,6 @@
       <c r="J155" t="n">
         <v>28.07</v>
       </c>
-      <c r="K155" t="n">
-        <v/>
-      </c>
-      <c r="L155" t="n">
-        <v/>
-      </c>
-      <c r="M155" t="n">
-        <v/>
-      </c>
-      <c r="N155" t="n">
-        <v/>
-      </c>
-      <c r="O155" t="n">
-        <v/>
-      </c>
-      <c r="P155" t="n">
-        <v/>
-      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-02; 相对D0=3.39%</t>
@@ -11212,24 +8917,6 @@
       <c r="J156" t="n">
         <v>49.81</v>
       </c>
-      <c r="K156" t="n">
-        <v/>
-      </c>
-      <c r="L156" t="n">
-        <v/>
-      </c>
-      <c r="M156" t="n">
-        <v/>
-      </c>
-      <c r="N156" t="n">
-        <v/>
-      </c>
-      <c r="O156" t="n">
-        <v/>
-      </c>
-      <c r="P156" t="n">
-        <v/>
-      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-02; 相对D0=-1.46%</t>
@@ -11281,24 +8968,12 @@
       <c r="J157" s="4" t="n">
         <v>199.13</v>
       </c>
-      <c r="K157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P157" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K157" s="4" t="n"/>
+      <c r="L157" s="4" t="n"/>
+      <c r="M157" s="4" t="n"/>
+      <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
+      <c r="P157" s="4" t="n"/>
       <c r="Q157" s="4" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-02; 相对D0=5.36%</t>
@@ -11350,24 +9025,6 @@
       <c r="J158" t="n">
         <v>1029.21</v>
       </c>
-      <c r="K158" t="n">
-        <v/>
-      </c>
-      <c r="L158" t="n">
-        <v/>
-      </c>
-      <c r="M158" t="n">
-        <v/>
-      </c>
-      <c r="N158" t="n">
-        <v/>
-      </c>
-      <c r="O158" t="n">
-        <v/>
-      </c>
-      <c r="P158" t="n">
-        <v/>
-      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-02; 相对D0=13.72%</t>
@@ -11419,24 +9076,6 @@
       <c r="J159" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="K159" t="n">
-        <v/>
-      </c>
-      <c r="L159" t="n">
-        <v/>
-      </c>
-      <c r="M159" t="n">
-        <v/>
-      </c>
-      <c r="N159" t="n">
-        <v/>
-      </c>
-      <c r="O159" t="n">
-        <v/>
-      </c>
-      <c r="P159" t="n">
-        <v/>
-      </c>
       <c r="Q159" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-02; 相对D0=-1.03%</t>
@@ -11488,24 +9127,6 @@
       <c r="J160" t="n">
         <v>222.7801</v>
       </c>
-      <c r="K160" t="n">
-        <v/>
-      </c>
-      <c r="L160" t="n">
-        <v/>
-      </c>
-      <c r="M160" t="n">
-        <v/>
-      </c>
-      <c r="N160" t="n">
-        <v/>
-      </c>
-      <c r="O160" t="n">
-        <v/>
-      </c>
-      <c r="P160" t="n">
-        <v/>
-      </c>
       <c r="Q160" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-02; 相对D0=-0.70%</t>
@@ -11557,24 +9178,12 @@
       <c r="J161" s="4" t="n">
         <v>72.565</v>
       </c>
-      <c r="K161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
       <c r="Q161" s="4" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-02; 相对D0=8.48%</t>
@@ -11626,24 +9235,12 @@
       <c r="J162" s="4" t="n">
         <v>59.305</v>
       </c>
-      <c r="K162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P162" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K162" s="4" t="n"/>
+      <c r="L162" s="4" t="n"/>
+      <c r="M162" s="4" t="n"/>
+      <c r="N162" s="4" t="n"/>
+      <c r="O162" s="4" t="n"/>
+      <c r="P162" s="4" t="n"/>
       <c r="Q162" s="4" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-02; 相对D0=0.65%</t>
@@ -11695,24 +9292,6 @@
       <c r="J163" t="n">
         <v>13.89</v>
       </c>
-      <c r="K163" t="n">
-        <v/>
-      </c>
-      <c r="L163" t="n">
-        <v/>
-      </c>
-      <c r="M163" t="n">
-        <v/>
-      </c>
-      <c r="N163" t="n">
-        <v/>
-      </c>
-      <c r="O163" t="n">
-        <v/>
-      </c>
-      <c r="P163" t="n">
-        <v/>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-02; 相对D0=0.00%</t>
@@ -11764,24 +9343,6 @@
       <c r="J164" t="n">
         <v>15.27</v>
       </c>
-      <c r="K164" t="n">
-        <v/>
-      </c>
-      <c r="L164" t="n">
-        <v/>
-      </c>
-      <c r="M164" t="n">
-        <v/>
-      </c>
-      <c r="N164" t="n">
-        <v/>
-      </c>
-      <c r="O164" t="n">
-        <v/>
-      </c>
-      <c r="P164" t="n">
-        <v/>
-      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-02; 相对D0=-1.99%</t>
@@ -11833,24 +9394,12 @@
       <c r="J165" s="4" t="n">
         <v>19.36</v>
       </c>
-      <c r="K165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P165" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K165" s="4" t="n"/>
+      <c r="L165" s="4" t="n"/>
+      <c r="M165" s="4" t="n"/>
+      <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
+      <c r="P165" s="4" t="n"/>
       <c r="Q165" s="4" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-02; 相对D0=9.88%</t>
@@ -11902,24 +9451,6 @@
       <c r="J166" t="n">
         <v>333.01</v>
       </c>
-      <c r="K166" t="n">
-        <v/>
-      </c>
-      <c r="L166" t="n">
-        <v/>
-      </c>
-      <c r="M166" t="n">
-        <v/>
-      </c>
-      <c r="N166" t="n">
-        <v/>
-      </c>
-      <c r="O166" t="n">
-        <v/>
-      </c>
-      <c r="P166" t="n">
-        <v/>
-      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-02; 相对D0=2.97%</t>
@@ -11970,24 +9501,6 @@
       </c>
       <c r="J167" t="n">
         <v>143.2</v>
-      </c>
-      <c r="K167" t="n">
-        <v/>
-      </c>
-      <c r="L167" t="n">
-        <v/>
-      </c>
-      <c r="M167" t="n">
-        <v/>
-      </c>
-      <c r="N167" t="n">
-        <v/>
-      </c>
-      <c r="O167" t="n">
-        <v/>
-      </c>
-      <c r="P167" t="n">
-        <v/>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -12225,24 +9738,12 @@
       <c r="J179" s="4" t="n">
         <v>40.03</v>
       </c>
-      <c r="K179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O179" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P179" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
+      <c r="P179" s="4" t="n"/>
       <c r="Q179" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-02; 相对D0=-3.47%</t>
@@ -12263,7 +9764,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -12290,24 +9790,6 @@
       <c r="J180" t="n">
         <v>89.06999999999999</v>
       </c>
-      <c r="K180" t="n">
-        <v/>
-      </c>
-      <c r="L180" t="n">
-        <v/>
-      </c>
-      <c r="M180" t="n">
-        <v/>
-      </c>
-      <c r="N180" t="n">
-        <v/>
-      </c>
-      <c r="O180" t="n">
-        <v/>
-      </c>
-      <c r="P180" t="n">
-        <v/>
-      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-02; 相对D0=-1.73%</t>
@@ -12359,24 +9841,12 @@
       <c r="J181" s="4" t="n">
         <v>188.07</v>
       </c>
-      <c r="K181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P181" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
       <c r="Q181" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-02; 相对D0=1.82%</t>
@@ -12428,24 +9898,12 @@
       <c r="J182" s="4" t="n">
         <v>139.02</v>
       </c>
-      <c r="K182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P182" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="n"/>
+      <c r="M182" s="4" t="n"/>
+      <c r="N182" s="4" t="n"/>
+      <c r="O182" s="4" t="n"/>
+      <c r="P182" s="4" t="n"/>
       <c r="Q182" s="4" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-02; 相对D0=2.07%</t>
@@ -12497,24 +9955,6 @@
       <c r="J183" t="n">
         <v>398.56</v>
       </c>
-      <c r="K183" t="n">
-        <v/>
-      </c>
-      <c r="L183" t="n">
-        <v/>
-      </c>
-      <c r="M183" t="n">
-        <v/>
-      </c>
-      <c r="N183" t="n">
-        <v/>
-      </c>
-      <c r="O183" t="n">
-        <v/>
-      </c>
-      <c r="P183" t="n">
-        <v/>
-      </c>
       <c r="Q183" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-02; 相对D0=29.68%</t>
@@ -12566,24 +10006,12 @@
       <c r="J184" s="4" t="n">
         <v>59.305</v>
       </c>
-      <c r="K184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O184" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P184" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K184" s="4" t="n"/>
+      <c r="L184" s="4" t="n"/>
+      <c r="M184" s="4" t="n"/>
+      <c r="N184" s="4" t="n"/>
+      <c r="O184" s="4" t="n"/>
+      <c r="P184" s="4" t="n"/>
       <c r="Q184" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-02; 相对D0=3.21%</t>
@@ -12635,24 +10063,12 @@
       <c r="J185" s="4" t="n">
         <v>13.885</v>
       </c>
-      <c r="K185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P185" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
+      <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
+      <c r="P185" s="4" t="n"/>
       <c r="Q185" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-02; 相对D0=4.01%</t>
@@ -12704,24 +10120,12 @@
       <c r="J186" s="4" t="n">
         <v>58.075</v>
       </c>
-      <c r="K186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O186" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P186" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K186" s="4" t="n"/>
+      <c r="L186" s="4" t="n"/>
+      <c r="M186" s="4" t="n"/>
+      <c r="N186" s="4" t="n"/>
+      <c r="O186" s="4" t="n"/>
+      <c r="P186" s="4" t="n"/>
       <c r="Q186" s="4" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-02; 相对D0=0.39%</t>
@@ -12773,24 +10177,12 @@
       <c r="J187" s="4" t="n">
         <v>56.365</v>
       </c>
-      <c r="K187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P187" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
+      <c r="P187" s="4" t="n"/>
       <c r="Q187" s="4" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-02; 相对D0=-0.24%</t>
@@ -12842,24 +10234,6 @@
       <c r="J188" t="n">
         <v>143.2</v>
       </c>
-      <c r="K188" t="n">
-        <v/>
-      </c>
-      <c r="L188" t="n">
-        <v/>
-      </c>
-      <c r="M188" t="n">
-        <v/>
-      </c>
-      <c r="N188" t="n">
-        <v/>
-      </c>
-      <c r="O188" t="n">
-        <v/>
-      </c>
-      <c r="P188" t="n">
-        <v/>
-      </c>
       <c r="Q188" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-02; 相对D0=13.28%</t>
@@ -12911,24 +10285,12 @@
       <c r="J189" s="4" t="n">
         <v>110.66</v>
       </c>
-      <c r="K189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P189" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="n"/>
+      <c r="M189" s="4" t="n"/>
+      <c r="N189" s="4" t="n"/>
+      <c r="O189" s="4" t="n"/>
+      <c r="P189" s="4" t="n"/>
       <c r="Q189" s="4" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-02; 相对D0=-4.36%</t>
@@ -12980,24 +10342,6 @@
       <c r="J190" t="n">
         <v>273.24</v>
       </c>
-      <c r="K190" t="n">
-        <v/>
-      </c>
-      <c r="L190" t="n">
-        <v/>
-      </c>
-      <c r="M190" t="n">
-        <v/>
-      </c>
-      <c r="N190" t="n">
-        <v/>
-      </c>
-      <c r="O190" t="n">
-        <v/>
-      </c>
-      <c r="P190" t="n">
-        <v/>
-      </c>
       <c r="Q190" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-02; 相对D0=-4.56%</t>
@@ -13049,24 +10393,12 @@
       <c r="J191" s="4" t="n">
         <v>198.16</v>
       </c>
-      <c r="K191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P191" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
+      <c r="P191" s="4" t="n"/>
       <c r="Q191" s="4" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-02; 相对D0=8.30%</t>
@@ -13118,24 +10450,6 @@
       <c r="J192" t="n">
         <v>504.21</v>
       </c>
-      <c r="K192" t="n">
-        <v/>
-      </c>
-      <c r="L192" t="n">
-        <v/>
-      </c>
-      <c r="M192" t="n">
-        <v/>
-      </c>
-      <c r="N192" t="n">
-        <v/>
-      </c>
-      <c r="O192" t="n">
-        <v/>
-      </c>
-      <c r="P192" t="n">
-        <v/>
-      </c>
       <c r="Q192" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-02; 相对D0=4.90%</t>
@@ -13187,24 +10501,12 @@
       <c r="J193" s="4" t="n">
         <v>112.31</v>
       </c>
-      <c r="K193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P193" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="n"/>
+      <c r="M193" s="4" t="n"/>
+      <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
+      <c r="P193" s="4" t="n"/>
       <c r="Q193" s="4" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-02; 相对D0=21.64%</t>
@@ -13256,24 +10558,12 @@
       <c r="J194" s="4" t="n">
         <v>75.175</v>
       </c>
-      <c r="K194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P194" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K194" s="4" t="n"/>
+      <c r="L194" s="4" t="n"/>
+      <c r="M194" s="4" t="n"/>
+      <c r="N194" s="4" t="n"/>
+      <c r="O194" s="4" t="n"/>
+      <c r="P194" s="4" t="n"/>
       <c r="Q194" s="4" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-02; 相对D0=8.07%</t>
@@ -13325,24 +10615,12 @@
       <c r="J195" s="4" t="n">
         <v>300.805</v>
       </c>
-      <c r="K195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O195" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P195" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
+      <c r="P195" s="4" t="n"/>
       <c r="Q195" s="4" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-02; 相对D0=5.55%</t>
@@ -13394,24 +10672,12 @@
       <c r="J196" s="4" t="n">
         <v>188.95</v>
       </c>
-      <c r="K196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P196" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K196" s="4" t="n"/>
+      <c r="L196" s="4" t="n"/>
+      <c r="M196" s="4" t="n"/>
+      <c r="N196" s="4" t="n"/>
+      <c r="O196" s="4" t="n"/>
+      <c r="P196" s="4" t="n"/>
       <c r="Q196" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-02; 相对D0=10.07%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -13463,24 +10729,12 @@
       <c r="J197" s="4" t="n">
         <v>421.51</v>
       </c>
-      <c r="K197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P197" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="n"/>
+      <c r="M197" s="4" t="n"/>
+      <c r="N197" s="4" t="n"/>
+      <c r="O197" s="4" t="n"/>
+      <c r="P197" s="4" t="n"/>
       <c r="Q197" s="4" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-02; 相对D0=16.61%</t>
@@ -13532,24 +10786,12 @@
       <c r="J198" s="4" t="n">
         <v>28.07</v>
       </c>
-      <c r="K198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P198" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="n"/>
+      <c r="M198" s="4" t="n"/>
+      <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
+      <c r="P198" s="4" t="n"/>
       <c r="Q198" s="4" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-02; 相对D0=48.68%</t>
@@ -13601,24 +10843,6 @@
       <c r="J199" t="n">
         <v>107.36</v>
       </c>
-      <c r="K199" t="n">
-        <v/>
-      </c>
-      <c r="L199" t="n">
-        <v/>
-      </c>
-      <c r="M199" t="n">
-        <v/>
-      </c>
-      <c r="N199" t="n">
-        <v/>
-      </c>
-      <c r="O199" t="n">
-        <v/>
-      </c>
-      <c r="P199" t="n">
-        <v/>
-      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-02; 相对D0=-6.38%</t>
@@ -13670,24 +10894,12 @@
       <c r="J200" s="4" t="n">
         <v>133.87</v>
       </c>
-      <c r="K200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O200" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P200" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K200" s="4" t="n"/>
+      <c r="L200" s="4" t="n"/>
+      <c r="M200" s="4" t="n"/>
+      <c r="N200" s="4" t="n"/>
+      <c r="O200" s="4" t="n"/>
+      <c r="P200" s="4" t="n"/>
       <c r="Q200" s="4" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-02; 相对D0=-0.16%</t>
@@ -13739,24 +10951,12 @@
       <c r="J201" s="4" t="n">
         <v>274.32</v>
       </c>
-      <c r="K201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O201" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P201" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
+      <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
+      <c r="P201" s="4" t="n"/>
       <c r="Q201" s="4" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-02; 相对D0=7.48%</t>
@@ -13808,24 +11008,6 @@
       <c r="J202" t="n">
         <v>116.605</v>
       </c>
-      <c r="K202" t="n">
-        <v/>
-      </c>
-      <c r="L202" t="n">
-        <v/>
-      </c>
-      <c r="M202" t="n">
-        <v/>
-      </c>
-      <c r="N202" t="n">
-        <v/>
-      </c>
-      <c r="O202" t="n">
-        <v/>
-      </c>
-      <c r="P202" t="n">
-        <v/>
-      </c>
       <c r="Q202" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-02; 相对D0=10.37%</t>
@@ -13877,24 +11059,12 @@
       <c r="J203" s="4" t="n">
         <v>188.95</v>
       </c>
-      <c r="K203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O203" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P203" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K203" s="4" t="n"/>
+      <c r="L203" s="4" t="n"/>
+      <c r="M203" s="4" t="n"/>
+      <c r="N203" s="4" t="n"/>
+      <c r="O203" s="4" t="n"/>
+      <c r="P203" s="4" t="n"/>
       <c r="Q203" s="4" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-02; 相对D0=15.86%</t>
@@ -13946,24 +11116,6 @@
       <c r="J204" t="n">
         <v>66.33</v>
       </c>
-      <c r="K204" t="n">
-        <v/>
-      </c>
-      <c r="L204" t="n">
-        <v/>
-      </c>
-      <c r="M204" t="n">
-        <v/>
-      </c>
-      <c r="N204" t="n">
-        <v/>
-      </c>
-      <c r="O204" t="n">
-        <v/>
-      </c>
-      <c r="P204" t="n">
-        <v/>
-      </c>
       <c r="Q204" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-02; 相对D0=2.66%</t>
@@ -14015,24 +11167,12 @@
       <c r="J205" s="4" t="n">
         <v>142.725</v>
       </c>
-      <c r="K205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P205" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
+      <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
+      <c r="P205" s="4" t="n"/>
       <c r="Q205" s="4" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-02; 相对D0=5.15%</t>
@@ -14084,24 +11224,6 @@
       <c r="J206" t="n">
         <v>600.47</v>
       </c>
-      <c r="K206" t="n">
-        <v/>
-      </c>
-      <c r="L206" t="n">
-        <v/>
-      </c>
-      <c r="M206" t="n">
-        <v/>
-      </c>
-      <c r="N206" t="n">
-        <v/>
-      </c>
-      <c r="O206" t="n">
-        <v/>
-      </c>
-      <c r="P206" t="n">
-        <v/>
-      </c>
       <c r="Q206" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-02; 相对D0=0.00%</t>
@@ -14153,24 +11275,12 @@
       <c r="J207" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="K207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P207" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
+      <c r="P207" s="4" t="n"/>
       <c r="Q207" s="4" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-02; 相对D0=3.74%</t>
@@ -14221,24 +11331,6 @@
       </c>
       <c r="J208" t="n">
         <v>420.1601</v>
-      </c>
-      <c r="K208" t="n">
-        <v/>
-      </c>
-      <c r="L208" t="n">
-        <v/>
-      </c>
-      <c r="M208" t="n">
-        <v/>
-      </c>
-      <c r="N208" t="n">
-        <v/>
-      </c>
-      <c r="O208" t="n">
-        <v/>
-      </c>
-      <c r="P208" t="n">
-        <v/>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -14336,7 +11428,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14348,7 +11439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14956,7 +12047,6 @@
       <c r="M12" s="20" t="n">
         <v>0.032532</v>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14985,7 +12075,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -15060,7 +12149,6 @@
       <c r="M14" s="18" t="n">
         <v>-0.021901</v>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15089,7 +12177,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -15141,7 +12228,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -15160,7 +12246,6 @@
       <c r="M16" s="20" t="n">
         <v>0.001613</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -15674,9 +12759,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -15722,9 +12805,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="21" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -15770,9 +12851,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="21" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -15818,9 +12897,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="21" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -15924,9 +13001,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15938,7 +13012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16185,7 +13259,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -16239,7 +13313,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -16415,7 +13489,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -16440,7 +13513,6 @@
       <c r="O9" s="20" t="n">
         <v>0.275555</v>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16469,7 +13541,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -16614,7 +13685,6 @@
       <c r="O12" s="20" t="n">
         <v>0.033441</v>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -16914,9 +13984,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="21" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -16968,9 +14036,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -17067,10 +14133,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17082,7 +14144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17481,7 +14543,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -17611,7 +14673,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -18681,7 +15742,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -18722,7 +15783,6 @@
       <c r="Q26" s="20" t="n">
         <v>0.036472</v>
       </c>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -18745,7 +15805,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -18865,7 +15925,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -19104,9 +16164,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -19164,9 +16222,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="21" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19224,9 +16280,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="21" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19284,9 +16338,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -19344,9 +16396,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19404,9 +16454,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="21" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19464,9 +16512,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="21" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -19595,8 +16641,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19608,7 +16652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19769,24 +16813,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19838,24 +16870,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19907,24 +16927,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19976,24 +16984,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20045,24 +17041,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20114,24 +17092,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20183,24 +17149,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20252,24 +17206,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20321,24 +17257,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20390,24 +17314,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20459,24 +17371,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20528,24 +17428,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20597,24 +17485,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20666,24 +17536,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20735,24 +17587,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20804,24 +17638,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20873,24 +17695,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -20942,24 +17752,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -21011,24 +17803,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -21265,24 +18045,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -21327,11 +18095,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21343,7 +18106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21504,7 +18267,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -21924,7 +18686,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -22340,7 +19101,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -22480,7 +19240,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -22826,7 +19585,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -22896,7 +19654,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -22966,7 +19723,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -23030,7 +19786,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -23106,7 +19862,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -23143,7 +19898,6 @@
       <c r="S26" s="18" t="n">
         <v>-0.013151</v>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -23166,7 +19920,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -23446,7 +20200,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -23516,7 +20270,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -23833,9 +20587,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23931,11 +20683,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25137,8 +21884,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
         <v>90</v>
       </c>
@@ -25319,7 +22064,6 @@
       <c r="V15" t="n">
         <v>245.9499053955078</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=63.20; 4H分金=62.40</t>
@@ -26391,8 +23135,6 @@
       <c r="T27" t="b">
         <v>0</v>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
         <v>91</v>
       </c>
@@ -27017,8 +23759,6 @@
       <c r="T34" t="b">
         <v>0</v>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
         <v>96</v>
       </c>
@@ -28407,7 +25147,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -28677,7 +25417,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -29607,7 +26347,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="8" t="n">
         <v>46164</v>
       </c>
@@ -29716,7 +26455,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -29876,7 +26614,6 @@
       <c r="D7" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="8" t="n">
         <v>46164</v>
       </c>
@@ -30424,7 +27161,6 @@
       <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" s="8" t="n">
         <v>46175</v>
       </c>
@@ -30593,7 +27329,6 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46175</v>
       </c>
@@ -31275,7 +28010,6 @@
       <c r="I23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" s="8" t="n">
         <v>46171</v>
       </c>
@@ -31387,7 +28121,6 @@
       <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" s="8" t="n">
         <v>46169</v>
       </c>
@@ -31615,7 +28348,6 @@
           <t>2026-05-22 (100), 2026-05-26 (80)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -31706,7 +28438,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -31740,7 +28472,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
@@ -31785,7 +28517,6 @@
           <t>2026-05-26 (88), 2026-06-01 (91)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -31849,7 +28580,6 @@
           <t>2026-05-28 (81)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -32459,7 +29189,6 @@
           <t>2026-05-22 (88), 2026-05-26 (93)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -32527,7 +29256,6 @@
           <t>2026-05-22 (91), 2026-05-26 (88)</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -32561,7 +29289,6 @@
           <t>2026-05-22 (86), 2026-05-26 (87)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -32654,8 +29381,6 @@
       <c r="F38" t="n">
         <v>314.82</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -32714,8 +29439,6 @@
       <c r="F40" t="n">
         <v>72.48</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -32744,8 +29467,6 @@
       <c r="F41" t="n">
         <v>11.65</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
@@ -32900,7 +29621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -32995,7 +29716,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -33189,14 +29910,12 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.84999999999999</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>-0.010349</v>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -33301,14 +30020,12 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.705</v>
       </c>
       <c r="I11" s="20" t="n">
         <v>0.00034</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -33417,14 +30134,12 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.27</v>
       </c>
       <c r="I14" s="18" t="n">
         <v>-0.019897</v>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -33544,7 +30259,6 @@
       <c r="I17" s="20" t="n">
         <v>0.029747</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -33974,9 +30688,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="21" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -34010,9 +30722,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="21" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -34050,9 +30760,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="21" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -34086,9 +30794,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -34122,9 +30828,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -34158,9 +30862,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -34194,9 +30896,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="21" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -34314,7 +31014,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34326,7 +31025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -34567,7 +31266,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -34816,7 +31515,6 @@
       <c r="K11" s="20" t="n">
         <v>0.088286</v>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -34983,7 +31681,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -34996,7 +31693,6 @@
       <c r="K15" s="20" t="n">
         <v>0.06015</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -35164,9 +31860,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -35206,9 +31900,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="21" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -35248,9 +31940,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="21" t="n"/>
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -35290,9 +31980,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="21" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -35336,9 +32024,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="21" t="n"/>
       <c r="C31" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -35378,9 +32064,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="21" t="n"/>
       <c r="C32" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -35420,9 +32104,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -35462,9 +32144,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -35504,9 +32184,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -35630,7 +32308,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
